--- a/Test Cases for OrangeHRM-My Info Module.xlsx
+++ b/Test Cases for OrangeHRM-My Info Module.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Test Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12FCBD9-1E1F-46D0-B4D4-E8540838D93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17BC7EC-3462-4E3F-A1AA-F289BF3E22AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB046A70-01F9-459A-BFBD-F1D77F648E09}"/>
   </bookViews>
@@ -51,18 +51,9 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>Test Senario</t>
-  </si>
-  <si>
-    <t>Pre-Condition</t>
-  </si>
-  <si>
     <t>Test Data</t>
   </si>
   <si>
-    <t>Post Condition</t>
-  </si>
-  <si>
     <t>Module Name</t>
   </si>
   <si>
@@ -94,9 +85,6 @@
   </si>
   <si>
     <t>Successful Employee login to OrangeHRM portal</t>
-  </si>
-  <si>
-    <t>TC-MI-01</t>
   </si>
   <si>
     <t>Username: Admin
@@ -112,16 +100,7 @@
     <t>User logged in successfully</t>
   </si>
   <si>
-    <t>TC-MI-02</t>
-  </si>
-  <si>
     <t>1. Orange HRM 3.0 site is launched on the browser</t>
-  </si>
-  <si>
-    <t>TC-MI-03</t>
-  </si>
-  <si>
-    <t>TC-MI-04</t>
   </si>
   <si>
     <t>Username: ABC
@@ -165,9 +144,6 @@
   </si>
   <si>
     <t>TC-LOG-04</t>
-  </si>
-  <si>
-    <t>TC-MI-05</t>
   </si>
   <si>
     <t>"My Info" page should open and display employee details (name, employee ID, etc.)</t>
@@ -347,18 +323,6 @@
     <t>All sections navigated successfully</t>
   </si>
   <si>
-    <t>TC-MI-06</t>
-  </si>
-  <si>
-    <t>TC-MI-07</t>
-  </si>
-  <si>
-    <t>TC-MI-08</t>
-  </si>
-  <si>
-    <t>TC-MI-09</t>
-  </si>
-  <si>
     <t>1. User is on "My Info" page</t>
   </si>
   <si>
@@ -406,6 +370,42 @@
   </si>
   <si>
     <t>Display error messages on unsuccessful login</t>
+  </si>
+  <si>
+    <t>Test Scenario</t>
+  </si>
+  <si>
+    <t>Pre-Conditions</t>
+  </si>
+  <si>
+    <t>Post Conditions</t>
+  </si>
+  <si>
+    <t>TC-MIM-01</t>
+  </si>
+  <si>
+    <t>TC-MIM-02</t>
+  </si>
+  <si>
+    <t>TC-MIM-05</t>
+  </si>
+  <si>
+    <t>TC-MIM-06</t>
+  </si>
+  <si>
+    <t>TC-MIM-07</t>
+  </si>
+  <si>
+    <t>TC-MIM-08</t>
+  </si>
+  <si>
+    <t>TC-MIM-09</t>
+  </si>
+  <si>
+    <t>TC-MIM-03</t>
+  </si>
+  <si>
+    <t>TC-MIM-04</t>
   </si>
 </sst>
 </file>
@@ -676,6 +676,33 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -687,33 +714,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -722,6 +722,26 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{9D7623A0-BE1E-4531-A9C8-B02A46BB3D81}"/>
   </cellStyles>
   <dxfs count="24">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -734,16 +754,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -764,7 +774,9 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
+        <b val="0"/>
+        <i val="0"/>
+        <color theme="6" tint="0.39994506668294322"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -774,19 +786,7 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color theme="6" tint="0.39994506668294322"/>
+        <color rgb="FFFF0000"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -1359,102 +1359,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="21"/>
+      <c r="A1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="17"/>
+    </row>
+    <row r="3" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="17"/>
+    </row>
+    <row r="4" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="21"/>
-    </row>
-    <row r="3" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="18">
+        <v>45726</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="20"/>
+    </row>
+    <row r="5" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="21"/>
-    </row>
-    <row r="4" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="22">
-        <v>45726</v>
-      </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="24"/>
-    </row>
-    <row r="5" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="22">
+      <c r="B5" s="25"/>
+      <c r="C5" s="18">
         <v>45727</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="20"/>
     </row>
     <row r="6" spans="1:31" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -1477,496 +1477,496 @@
       <c r="AE6" s="5"/>
     </row>
     <row r="7" spans="1:31" s="6" customFormat="1" ht="12" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
     </row>
     <row r="8" spans="1:31" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>22</v>
-      </c>
       <c r="I9" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>109</v>
+        <v>31</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>97</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="12" t="s">
+      <c r="I10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="11" t="s">
+      <c r="B12" s="24"/>
+      <c r="C12" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" ht="72" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="11" t="s">
+      <c r="I12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="12" t="s">
         <v>25</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="H13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="I13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>44</v>
-      </c>
       <c r="J13" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>105</v>
+        <v>109</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>93</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="26"/>
+        <v>103</v>
+      </c>
+      <c r="B17" s="22"/>
       <c r="C17" s="11" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>107</v>
+        <v>104</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="27"/>
+        <v>105</v>
+      </c>
+      <c r="B19" s="23"/>
       <c r="C19" s="11" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="26"/>
+        <v>106</v>
+      </c>
+      <c r="B20" s="22"/>
       <c r="C20" s="11" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
@@ -1983,12 +1983,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="B10:B12"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A1:B1"/>
@@ -1997,37 +1991,43 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C1:K1"/>
     <mergeCell ref="C2:K2"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B10:B12"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="K8 J8:J1048576">
-    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
-      <formula>#REF!</formula>
+  <conditionalFormatting sqref="J6:J1048576">
+    <cfRule type="cellIs" dxfId="6" priority="27" operator="equal">
+      <formula>$J$14</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="25" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J8:J1048576 K8">
+    <cfRule type="cellIs" dxfId="5" priority="13" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J9:J19 J21">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>$J$9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>$J$9</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J20">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>$J$20</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J21 J9:J19">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>$J$9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>$J$9</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K8 J8:J1048576">
-    <cfRule type="cellIs" dxfId="1" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="25" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J1048576">
-    <cfRule type="cellIs" dxfId="0" priority="27" operator="equal">
-      <formula>$J$14</formula>
+    <cfRule type="cellIs" dxfId="0" priority="26" operator="equal">
+      <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2053,17 +2053,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
